--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳万达</t>
+          <t>华为智能生活馆•信阳西亚城</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
+          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳西亚城</t>
+          <t>华为智能生活馆•信阳万达</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
+          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -13125,22 +13125,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,29 +13150,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,29 +13214,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13246,29 +13246,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,29 +13278,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,29 +13310,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,14 +13374,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -13391,12 +13391,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,14 +13406,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -13423,12 +13423,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,29 +13438,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13482,17 +13482,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
@@ -13514,17 +13514,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
@@ -13546,17 +13546,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
@@ -13578,17 +13578,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13642,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
@@ -13674,17 +13674,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
@@ -13738,17 +13738,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -13770,17 +13770,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13790,29 +13790,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
@@ -13893,22 +13893,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13918,29 +13918,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,7 +13989,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14085,22 +14085,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -13125,7 +13125,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -13135,12 +13135,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -13162,17 +13162,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,29 +13182,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
@@ -13226,17 +13226,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13246,29 +13246,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
@@ -13290,17 +13290,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,29 +13310,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,29 +13374,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
@@ -13418,17 +13418,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13450,17 +13450,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,29 +13630,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13758,14 +13758,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13866,17 +13866,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13886,29 +13886,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13918,29 +13918,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,22 +13989,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14021,22 +14021,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14053,7 +14053,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -14063,12 +14063,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14085,22 +14085,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14117,22 +14117,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14149,7 +14149,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14250,17 +14250,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -13125,22 +13125,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,29 +13150,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,29 +13214,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13246,29 +13246,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,29 +13278,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,29 +13310,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
@@ -13354,17 +13354,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13386,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13418,17 +13418,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -13482,17 +13482,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,14 +13598,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,29 +13630,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13790,29 +13790,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13866,17 +13866,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13886,29 +13886,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13918,29 +13918,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13950,14 +13950,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,22 +13989,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14021,22 +14021,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14053,22 +14053,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14090,17 +14090,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14117,22 +14117,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14149,7 +14149,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14181,7 +14181,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -14191,12 +14191,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14213,22 +14213,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳西亚城</t>
+          <t>华为智能生活馆•信阳万达</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
+          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳万达</t>
+          <t>华为智能生活馆•信阳西亚城</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
+          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -13130,17 +13130,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
@@ -13162,17 +13162,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,29 +13182,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13253,22 +13253,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,29 +13278,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,29 +13310,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,29 +13374,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
@@ -13423,12 +13423,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13450,17 +13450,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,14 +13534,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13551,12 +13551,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,14 +13598,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13642,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
@@ -13802,17 +13802,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
@@ -13866,17 +13866,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13957,22 +13957,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,22 +13989,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14053,22 +14053,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14085,22 +14085,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14117,22 +14117,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14181,7 +14181,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -14191,12 +14191,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14213,22 +14213,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳万达</t>
+          <t>华为智能生活馆•信阳西亚城</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
+          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳西亚城</t>
+          <t>华为智能生活馆•信阳万达</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
+          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -13125,22 +13125,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,29 +13150,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -13226,17 +13226,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
@@ -13258,17 +13258,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,29 +13278,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13322,17 +13322,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13354,17 +13354,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13386,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
@@ -13418,17 +13418,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
@@ -13455,12 +13455,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13642,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13790,29 +13790,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13854,29 +13854,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
@@ -13957,22 +13957,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,22 +13989,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14053,22 +14053,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14085,22 +14085,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11262,7 +11262,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -13125,22 +13125,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,29 +13150,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13194,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,29 +13214,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13246,29 +13246,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,29 +13278,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,29 +13310,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,29 +13374,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,14 +13438,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13514,17 +13514,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,14 +13566,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13583,12 +13583,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
@@ -13610,17 +13610,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
@@ -13647,12 +13647,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,14 +13726,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13790,29 +13790,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13822,29 +13822,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13854,29 +13854,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -13957,22 +13957,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,22 +13989,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14021,22 +14021,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14053,7 +14053,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -14063,12 +14063,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14090,17 +14090,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14117,22 +14117,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3917,24 +3917,24 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>宾利</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>-1</v>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -3945,14 +3945,14 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" s="3" t="n">
         <v>0</v>
@@ -3966,14 +3966,14 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="3" t="n">
         <v>0</v>
@@ -3987,14 +3987,14 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="3" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -4323,14 +4323,14 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="3" t="n">
         <v>0</v>
@@ -4344,14 +4344,14 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="3" t="n">
         <v>0</v>
@@ -4365,59 +4365,59 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="C166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C167" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D166" s="2" t="n">
+      <c r="D167" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="E167" s="2" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -4428,14 +4428,14 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E168" s="3" t="n">
         <v>0</v>
@@ -4449,14 +4449,14 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E169" s="3" t="n">
         <v>0</v>
@@ -4470,14 +4470,14 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E170" s="3" t="n">
         <v>0</v>
@@ -4491,14 +4491,14 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E171" s="3" t="n">
         <v>0</v>
@@ -4512,14 +4512,14 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E172" s="3" t="n">
         <v>0</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E173" s="3" t="n">
         <v>0</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E174" s="3" t="n">
         <v>0</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="E176" s="3" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E177" s="3" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E178" s="3" t="n">
         <v>0</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E179" s="3" t="n">
         <v>0</v>
@@ -4680,38 +4680,38 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C180" s="3" t="n">
+      <c r="C181" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D180" s="3" t="n">
+      <c r="D181" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E180" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="E181" s="4" t="n">
-        <v>1</v>
+      <c r="E181" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E182" s="4" t="n">
         <v>1</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E183" s="4" t="n">
         <v>1</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E184" s="4" t="n">
         <v>1</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E185" s="4" t="n">
         <v>1</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E186" s="4" t="n">
         <v>1</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E187" s="4" t="n">
         <v>1</v>
@@ -4848,14 +4848,14 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E188" s="4" t="n">
         <v>1</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E189" s="4" t="n">
         <v>1</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E190" s="4" t="n">
         <v>1</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E191" s="4" t="n">
         <v>1</v>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="E193" s="4" t="n">
         <v>2</v>
@@ -4974,14 +4974,14 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="E194" s="4" t="n">
         <v>2</v>
@@ -4995,17 +4995,17 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -5016,38 +5016,38 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="E196" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E197" s="2" t="n">
-        <v>-1</v>
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -5058,14 +5058,14 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>-1</v>
@@ -5079,14 +5079,14 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>-1</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>-1</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>-1</v>
@@ -5142,38 +5142,38 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="inlineStr">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D203" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>0</v>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="204">
@@ -5184,14 +5184,14 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E204" s="3" t="n">
         <v>0</v>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E205" s="3" t="n">
         <v>0</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E206" s="3" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E207" s="3" t="n">
         <v>0</v>
@@ -5268,14 +5268,14 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E208" s="3" t="n">
         <v>0</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E209" s="3" t="n">
         <v>0</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E210" s="3" t="n">
         <v>0</v>
@@ -5331,14 +5331,14 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E211" s="3" t="n">
         <v>0</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E212" s="3" t="n">
         <v>0</v>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E213" s="3" t="n">
         <v>0</v>
@@ -5394,14 +5394,14 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="E214" s="3" t="n">
         <v>0</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="E215" s="3" t="n">
         <v>0</v>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E216" s="3" t="n">
         <v>0</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E217" s="3" t="n">
         <v>0</v>
@@ -5478,14 +5478,14 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E218" s="3" t="n">
         <v>0</v>
@@ -5499,14 +5499,14 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E219" s="3" t="n">
         <v>0</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E220" s="3" t="n">
         <v>0</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E221" s="3" t="n">
         <v>0</v>
@@ -5562,14 +5562,14 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E222" s="3" t="n">
         <v>0</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E223" s="3" t="n">
         <v>0</v>
@@ -5604,38 +5604,38 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C224" s="3" t="n">
+      <c r="C225" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="D225" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E224" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D225" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="E225" s="4" t="n">
-        <v>1</v>
+      <c r="E225" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -5646,38 +5646,38 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
           <t>宁夏</t>
         </is>
       </c>
-      <c r="C226" s="4" t="n">
+      <c r="C227" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D226" s="4" t="n">
+      <c r="D227" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E226" s="4" t="n">
+      <c r="E227" s="4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D227" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E227" s="2" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="228">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="229">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E229" s="2" t="n">
         <v>-1</v>
@@ -5730,38 +5730,38 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C231" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D231" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>0</v>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="232">
@@ -5772,14 +5772,14 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E232" s="3" t="n">
         <v>0</v>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E233" s="3" t="n">
         <v>0</v>
@@ -5814,14 +5814,14 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E234" s="3" t="n">
         <v>0</v>
@@ -5835,14 +5835,14 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E235" s="3" t="n">
         <v>0</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E236" s="3" t="n">
         <v>0</v>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E237" s="3" t="n">
         <v>0</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E238" s="3" t="n">
         <v>0</v>
@@ -5919,14 +5919,14 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E239" s="3" t="n">
         <v>0</v>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E240" s="3" t="n">
         <v>0</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E241" s="3" t="n">
         <v>0</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E242" s="3" t="n">
         <v>0</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E243" s="3" t="n">
         <v>0</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E244" s="3" t="n">
         <v>0</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E245" s="3" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E246" s="3" t="n">
         <v>0</v>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E247" s="3" t="n">
         <v>0</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E248" s="3" t="n">
         <v>0</v>
@@ -6129,14 +6129,14 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E249" s="3" t="n">
         <v>0</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E250" s="3" t="n">
         <v>0</v>
@@ -6171,14 +6171,14 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E251" s="3" t="n">
         <v>0</v>
@@ -6192,14 +6192,14 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E252" s="3" t="n">
         <v>0</v>
@@ -6213,14 +6213,14 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E253" s="3" t="n">
         <v>0</v>
@@ -6234,14 +6234,14 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E254" s="3" t="n">
         <v>0</v>
@@ -6255,14 +6255,14 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E255" s="3" t="n">
         <v>0</v>
@@ -6276,14 +6276,14 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C256" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E256" s="3" t="n">
         <v>0</v>
@@ -6297,14 +6297,14 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C257" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E257" s="3" t="n">
         <v>0</v>
@@ -6313,19 +6313,19 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C258" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E258" s="3" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="3" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -6486,14 +6486,14 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="3" t="n">
         <v>0</v>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="3" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="3" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -6633,38 +6633,38 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D274" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="E274" s="2" t="n">
-        <v>-1</v>
+      <c r="C274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>-1</v>
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>-1</v>
@@ -6717,38 +6717,38 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C278" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>0</v>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="D278" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="279">
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E279" s="3" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E281" s="3" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E284" s="3" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E285" s="3" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E286" s="3" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E287" s="3" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E290" s="3" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E291" s="3" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="E292" s="3" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="E293" s="3" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E294" s="3" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E295" s="3" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E296" s="3" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E297" s="3" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E298" s="3" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E299" s="3" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E300" s="3" t="n">
         <v>0</v>
@@ -7221,38 +7221,38 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E301" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C301" s="3" t="n">
+      <c r="C302" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D301" s="3" t="n">
+      <c r="D302" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E301" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C302" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D302" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E302" s="4" t="n">
-        <v>1</v>
+      <c r="E302" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C303" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D303" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E303" s="4" t="n">
         <v>1</v>
@@ -7284,38 +7284,38 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C304" s="4" t="n">
+      <c r="C305" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D304" s="4" t="n">
+      <c r="D305" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E304" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C305" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D305" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E305" s="3" t="n">
-        <v>0</v>
+      <c r="E305" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E306" s="3" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E307" s="3" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E308" s="3" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E309" s="3" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E310" s="3" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E311" s="3" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E312" s="3" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E313" s="3" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="E314" s="3" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E315" s="3" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="E316" s="3" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="E317" s="3" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E318" s="3" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E319" s="3" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="E320" s="3" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E321" s="3" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E322" s="3" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="E323" s="3" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="E324" s="3" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E325" s="3" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E326" s="3" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E327" s="3" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E328" s="3" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E329" s="3" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E330" s="3" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E331" s="3" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E332" s="3" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D333" s="3" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E333" s="3" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D334" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E334" s="3" t="n">
         <v>0</v>
@@ -7935,38 +7935,38 @@
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C335" s="3" t="n">
+      <c r="C336" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D335" s="3" t="n">
+      <c r="D336" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="E335" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C336" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D336" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E336" s="2" t="n">
-        <v>-1</v>
+      <c r="E336" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E337" s="2" t="n">
         <v>-1</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>-1</v>
@@ -8019,38 +8019,38 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="3" t="inlineStr">
+      <c r="A340" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B340" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C340" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D340" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E340" s="3" t="n">
-        <v>0</v>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="341">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D342" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E344" s="3" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E345" s="3" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E346" s="3" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E347" s="3" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E348" s="3" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E349" s="3" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E350" s="3" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E353" s="3" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E356" s="3" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E357" s="3" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E358" s="3" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E359" s="3" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E360" s="3" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E361" s="3" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E362" s="3" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
@@ -8544,14 +8544,14 @@
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E364" s="3" t="n">
         <v>0</v>
@@ -8565,14 +8565,14 @@
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E365" s="3" t="n">
         <v>0</v>
@@ -8581,12 +8581,12 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D367" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" s="3" t="n">
         <v>0</v>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D369" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E369" s="3" t="n">
         <v>0</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="3" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="3" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
@@ -8754,59 +8754,59 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>阿斯顿·马丁</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C374" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D374" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E374" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="2" t="inlineStr">
+      <c r="C375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
         <is>
           <t>雷克萨斯</t>
         </is>
       </c>
-      <c r="B375" s="2" t="inlineStr">
+      <c r="B376" s="2" t="inlineStr">
         <is>
           <t>天津</t>
         </is>
       </c>
-      <c r="C375" s="2" t="n">
+      <c r="C376" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D375" s="2" t="n">
+      <c r="D376" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E375" s="2" t="n">
+      <c r="E376" s="2" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="3" t="inlineStr">
-        <is>
-          <t>雷克萨斯</t>
-        </is>
-      </c>
-      <c r="B376" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C376" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D376" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E376" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E377" s="3" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E378" s="3" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E379" s="3" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E380" s="3" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E381" s="3" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E382" s="3" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E383" s="3" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E384" s="3" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E385" s="3" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E386" s="3" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E387" s="3" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E388" s="3" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E389" s="3" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E390" s="3" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E391" s="3" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E392" s="3" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E393" s="3" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E394" s="3" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E395" s="3" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E396" s="3" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E397" s="3" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E398" s="3" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E399" s="3" t="n">
         <v>0</v>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D400" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E400" s="3" t="n">
         <v>0</v>
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E401" s="3" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E402" s="3" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C403" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D403" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E403" s="3" t="n">
         <v>0</v>
@@ -9384,38 +9384,38 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C404" s="3" t="n">
+      <c r="C405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D404" s="3" t="n">
+      <c r="D405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E404" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C405" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D405" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="E405" s="2" t="n">
-        <v>-1</v>
+      <c r="E405" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,38 +9426,38 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E406" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="inlineStr">
+      <c r="A407" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C407" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="D407" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="E407" s="3" t="n">
-        <v>0</v>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E408" s="3" t="n">
         <v>0</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E409" s="3" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="E410" s="3" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,38 +9846,38 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D426" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E426" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C426" s="3" t="n">
+      <c r="C427" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D426" s="3" t="n">
+      <c r="D427" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="E426" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B427" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C427" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="D427" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="E427" s="4" t="n">
-        <v>1</v>
+      <c r="E427" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C428" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E428" s="4" t="n">
         <v>1</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C429" s="4" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>1</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,17 +10014,17 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E434" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -10035,16 +10035,37 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C435" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="D435" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="E435" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10065,7 +10086,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
@@ -10211,12 +10232,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Tianjin City</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -11262,7 +11283,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11277,7 +11298,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11294,7 +11315,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11309,7 +11330,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -13125,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13150,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13182,7 +13203,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
@@ -13194,17 +13215,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13214,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13246,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13278,7 +13299,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
@@ -13290,17 +13311,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13310,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13342,7 +13363,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
@@ -13354,17 +13375,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13374,7 +13395,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13407,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13406,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13438,14 +13459,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -13455,12 +13476,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13470,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13502,7 +13523,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
@@ -13514,17 +13535,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13534,14 +13555,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13551,12 +13572,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13566,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13598,7 +13619,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
@@ -13610,17 +13631,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13630,7 +13651,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
@@ -13647,12 +13668,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13662,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13694,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13726,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13758,29 +13779,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13790,7 +13811,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
@@ -13829,22 +13850,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13854,7 +13875,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
@@ -13893,22 +13914,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13918,29 +13939,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13950,29 +13971,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13989,22 +14010,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14021,22 +14042,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14085,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14117,22 +14138,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14154,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14186,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14213,22 +14234,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14245,7 +14266,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -14255,12 +14276,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11635,7 +11635,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳西亚城</t>
+          <t>华为智能生活馆•信阳万达</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
+          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳万达</t>
+          <t>华为智能生活馆•信阳西亚城</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
+          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
@@ -13215,17 +13215,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -13306,22 +13306,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13375,17 +13375,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14010,7 +14010,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14042,22 +14042,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14074,7 +14074,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -14084,12 +14084,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14138,22 +14138,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14202,22 +14202,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
@@ -13183,17 +13183,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -13279,17 +13279,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
@@ -13412,12 +13412,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,14 +13587,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13914,22 +13914,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14042,22 +14042,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14074,22 +14074,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14138,22 +14138,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14180,12 +14180,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14202,22 +14202,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14234,22 +14234,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
@@ -13183,17 +13183,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13279,17 +13279,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,14 +13459,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,14 +13555,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,14 +13715,14 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -13732,12 +13732,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>怀化仁达锦尚4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>怀化仁达锦尚卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14010,22 +14010,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14074,22 +14074,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚4S中心</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>怀化仁达锦尚卫星店</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14180,12 +14180,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14202,22 +14202,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14234,22 +14234,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260831_vs_20260907.xlsx
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>杭州杭行路</t>
+          <t>杭州滨江宝龙城</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
+          <t>浙江省杭州市滨江区滨盛路3867号</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>杭州滨江宝龙城</t>
+          <t>杭州杭行路</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区滨盛路3867号</t>
+          <t>浙江省杭州市拱墅区祥符街道杭行路208-14号</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳万达</t>
+          <t>华为智能生活馆•信阳西亚城</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
+          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•信阳西亚城</t>
+          <t>华为智能生活馆•信阳万达</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>河南省信阳市平桥区龙江大道与龙江东路交叉口西亚城华为智能生活馆</t>
+          <t>河南省信阳市平桥区羊山新区新七大道与新十四大街交汇处东南侧信阳羊山万达广场1F次主3号</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
+          <t>小鹏汽车郑州南三环销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
+          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
+          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
+          <t>小米汽车山东省菏泽市定陶区定陶小镇</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
+          <t>山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北 50 米路东（定陶新能源汽车小镇 / 定陶汽车小镇园区内） → 山东省菏泽市定陶区杜堂镇广州路与向阳路交叉口往北50米路东（定陶新能源汽车小镇/定陶汽车小镇园区内）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安未央北辰大道销售中心</t>
+          <t>小米汽车山东省济南市历城区经十东路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
+          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>深圳奥泽汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
+          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东莞高埗销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
+          <t>日新东路259号 西山区 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街服务中心</t>
+          <t>广东中奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(南京慧成街店) → 雨合路15号-1号</t>
+          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E → 日圆二里1号湾悦城L1-033A/033B/033C/035E/036A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
+          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
+          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,14 +13491,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
+          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉奥兴用户中心</t>
+          <t>小米汽车湖北省武汉市洪山区张家湾国际汽车科技园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
+          <t>烽火路特一号张家湾国际汽车科技园1楼2号 → 小米汽车销售服务中心·武汉洪山张家湾贤良汽车园店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蚌埠安迪汽车销售服务有限公司</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
+          <t>前进街道黄埔大道东663号 → 黄埔大道东657号201-204自编之一铺</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
+          <t>广东省梅州市梅县区广梅南路286-2号 → 广东省梅州市梅县区扶大高新区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十东路</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>经十东路与玉岭路交叉口 → 凤鸣路4661号融创停车楼1楼</t>
+          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车东营郝家汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>亳州市谯城区杜仲路与桐乡路交叉口北100米 → 安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧</t>
+          <t>山东省东营市垦利区董集镇北二路5号 → 山东省东营市垦利区北二路5号</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
+          <t>陕西省西安市浐灞生态区长鸣路与南三环十字东北角马腾空国际车城10113号商铺 → 西安市灞桥区红旗街道临湾路219号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕头龙湖销售服务中心</t>
+          <t>上汽奥迪武汉奥兴用户中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
+          <t>湖北省武汉市汉阳区江城大道369号 → 湖北省武汉市武汉经济技术开发区江城大道369号A3栋</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>深圳奥泽汽车销售服务有限公司</t>
+          <t>小鹏汽车西安未央北辰大道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,14 +13747,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区上梅林梅林路42号(孖岭地铁站E口步行280米) → 广东省深圳市罗湖区宝岗路241号</t>
+          <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅） → 陕西省西安市浐灞生态区欧亚一路1688号（新丰泰汽车园区内）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>广东中奥汽车销售服务有限公司</t>
+          <t>小鹏汽车汕头龙湖销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区石井凰岗凤凰大街1号 → 广东省广州市白云区石井凰岗牌坊(左侧)</t>
+          <t>汕头市龙湖区南山路居委长平路与泰山路交界东北侧“车展”西北角20号 → 汕头市龙湖区汕汾路与淮河路交界处北侧之一（东侧）</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州南三环销售服务中心</t>
+          <t>小鹏汽车东莞高埗销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区文治路20号2号楼1层112号 → 河南省郑州市管城回族区文治路与鼎尚街交叉口小鹏汽车南三环销售服务中心</t>
+          <t>广东省东莞市高埗镇高昌路5号 → 广东省东莞市高埗镇高昌路5号101室小鹏汽车高埗销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>蚌埠安迪汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>安徽省蚌埠市禹会区国际汽车城1号蚌埠 → 安徽省蚌埠市禹会区迎宾大道国际汽车城24号</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州东部汽车城销售服务中心</t>
+          <t>小鹏汽车莆田城涵东大道销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市管城回族区航海路北第七大街东1386号小鹏汽车 → 河南自贸试验区郑州片区（经开）航海路北、第七大街东1388号</t>
+          <t>福建省莆田市涵江区白塘镇埭里村城涵东大道2888号 → 福建省莆田市城厢区华亭镇荔华东大道2899号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省温州市瓯海区瓯海万象城汽车体验店</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>瓯越大道1999号 → 浙江省温州市瓯海区瓯越大道1999号</t>
+          <t>海南省琼海市嘉积镇豪华路59号小鹏汽车 → 海南省琼海市嘉积镇豪华路59号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道 → 小米汽车河南省信阳市平桥区南京大道销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心 → 小鹏汽车上海浦东金桥销售中心</t>
         </is>
       </c>
     </row>
@@ -14010,22 +14010,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>北京中诚海华4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上海复地活力城城市展厅L1047</t>
+          <t>北京中诚海华维修中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14042,22 +14042,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂4S中心</t>
+          <t>蔚来空间 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上海中升沃茂维修中心</t>
+          <t>蔚来体验中心 | 沭阳汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14074,22 +14074,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区苏宁广场</t>
+          <t>小鹏汽车靖江吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
+          <t>小鹏汽车靖江国际汽车城销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华4S中心</t>
+          <t>小米汽车浙江绍兴越城区苏宁广场</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>北京中诚海华维修中心</t>
+          <t>小米之家浙江省绍兴市越城区苏宁广场汽车体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14138,22 +14138,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦维修中心</t>
+          <t>华为智能生活馆•合肥方圆荟</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>淮安达发星悦4S中心</t>
+          <t>华为智能生活馆•合肥方圆LIVE</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14180,12 +14180,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江吾悦广场销售展厅</t>
+          <t>淮安达发星悦维修中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车靖江国际汽车城销售展厅</t>
+          <t>淮安达发星悦4S中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14202,22 +14202,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 沭阳汽车城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 沭阳汽车城</t>
+          <t>上海复地活力城城市展厅L1047</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14234,22 +14234,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆荟</t>
+          <t>小米汽车江苏南京市秦淮区大明路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥方圆LIVE</t>
+          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市秦淮区大明路</t>
+          <t>上海中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市秦淮区大明路销售服务中心</t>
+          <t>上海中升沃茂维修中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
